--- a/src/test/resources/testdata/LoginTestData.xlsx
+++ b/src/test/resources/testdata/LoginTestData.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AutomationFramework2026\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{167ACFFC-39C8-47CF-95BF-CDC5BF59E2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D9C334-A2F5-4C8D-B40D-C1AEA2DD5CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3A06D00D-A48A-4996-92A4-3C1EA70AC801}"/>
   </bookViews>
   <sheets>
-    <sheet name="testdata" sheetId="1" r:id="rId1"/>
+    <sheet name="LoginData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
